--- a/artfynd/A 27519-2026 artfynd.xlsx
+++ b/artfynd/A 27519-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129920255</v>
+        <v>129920246</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729689</v>
+        <v>729791</v>
       </c>
       <c r="R2" t="n">
-        <v>7122797</v>
+        <v>7122551</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,30 +772,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129920263</v>
+        <v>129920248</v>
       </c>
       <c r="B3" t="n">
-        <v>91796</v>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -808,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729744</v>
+        <v>729725</v>
       </c>
       <c r="R3" t="n">
-        <v>7122685</v>
+        <v>7122755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129920247</v>
+        <v>129920249</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729742</v>
+        <v>729726</v>
       </c>
       <c r="R4" t="n">
-        <v>7122682</v>
+        <v>7122755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920256</v>
+        <v>129920250</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729688</v>
+        <v>729727</v>
       </c>
       <c r="R5" t="n">
-        <v>7122792</v>
+        <v>7122757</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1069,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920249</v>
+        <v>129920262</v>
       </c>
       <c r="B6" t="n">
-        <v>80230</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1104,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729726</v>
+        <v>729742</v>
       </c>
       <c r="R6" t="n">
-        <v>7122755</v>
+        <v>7122879</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920246</v>
+        <v>129920247</v>
       </c>
       <c r="B7" t="n">
-        <v>91776</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729791</v>
+        <v>729742</v>
       </c>
       <c r="R7" t="n">
-        <v>7122551</v>
+        <v>7122682</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920260</v>
+        <v>129920251</v>
       </c>
       <c r="B8" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729692</v>
+        <v>729683</v>
       </c>
       <c r="R8" t="n">
-        <v>7122773</v>
+        <v>7122900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129920254</v>
+        <v>129920252</v>
       </c>
       <c r="B9" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,7 +1397,7 @@
         <v>729688</v>
       </c>
       <c r="R9" t="n">
-        <v>7122802</v>
+        <v>7122888</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920257</v>
+        <v>129920253</v>
       </c>
       <c r="B10" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729683</v>
+        <v>729679</v>
       </c>
       <c r="R10" t="n">
-        <v>7122772</v>
+        <v>7122879</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920248</v>
+        <v>129920254</v>
       </c>
       <c r="B11" t="n">
-        <v>80230</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1604,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729725</v>
+        <v>729688</v>
       </c>
       <c r="R11" t="n">
-        <v>7122755</v>
+        <v>7122802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1640,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1666,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129920262</v>
+        <v>129920255</v>
       </c>
       <c r="B12" t="n">
-        <v>80326</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1677,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1701,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729742</v>
+        <v>729689</v>
       </c>
       <c r="R12" t="n">
-        <v>7122879</v>
+        <v>7122797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1737,6 +1736,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1763,32 +1767,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129920250</v>
+        <v>129920256</v>
       </c>
       <c r="B13" t="n">
-        <v>80230</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1798,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729727</v>
+        <v>729688</v>
       </c>
       <c r="R13" t="n">
-        <v>7122757</v>
+        <v>7122792</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1834,6 +1838,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1860,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129920251</v>
+        <v>129920257</v>
       </c>
       <c r="B14" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,7 +1907,7 @@
         <v>729683</v>
       </c>
       <c r="R14" t="n">
-        <v>7122900</v>
+        <v>7122772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,7 +1974,7 @@
         <v>129920258</v>
       </c>
       <c r="B15" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129920252</v>
+        <v>129920260</v>
       </c>
       <c r="B16" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2099,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729688</v>
+        <v>729692</v>
       </c>
       <c r="R16" t="n">
-        <v>7122888</v>
+        <v>7122773</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,6 +2172,108 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129920261</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>729692</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7122525</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27519-2026 artfynd.xlsx
+++ b/artfynd/A 27519-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920246</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920249</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920250</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920262</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920247</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920251</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920252</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920253</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920254</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920255</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920256</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920257</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920258</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920260</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2274,8 +2354,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129920261</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>